--- a/Docs/Lab02/Lab02_BBT_TCs_Form.xlsx
+++ b/Docs/Lab02/Lab02_BBT_TCs_Form.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000" firstSheet="1" activeTab="1"/>
+    <workbookView windowWidth="23040" windowHeight="9000" firstSheet="1"/>
   </bookViews>
   <sheets>
     <sheet name="Statement" sheetId="1" r:id="rId1"/>
@@ -118,7 +118,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="142">
   <si>
     <t>VVSS, Info Romana, 2025-2026</t>
   </si>
@@ -166,9 +166,6 @@
   </si>
   <si>
     <t>1. Evidenţa produselor din MyDrinkShop</t>
-  </si>
-  <si>
-    <t>Un cinefil doreşte să îşi dezvolte un program pentru gestionarea filmelor din colecţia personală. Programul va permite următoarele operaţii:</t>
   </si>
   <si>
     <r>
@@ -1057,20 +1054,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color indexed="10"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
       <i/>
       <sz val="11"/>
       <color rgb="FF0066CC"/>
@@ -1087,7 +1070,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color indexed="17"/>
+      <color indexed="10"/>
       <name val="Calibri"/>
       <charset val="134"/>
     </font>
@@ -1100,11 +1083,25 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="17"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="9"/>
       <name val="Tahoma"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="Tahoma"/>
       <charset val="134"/>
@@ -2020,7 +2017,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="182">
+  <cellXfs count="176">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2353,9 +2350,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2429,8 +2423,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -2447,15 +2439,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2859,18 +2842,18 @@
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="3"/>
-      <c r="H1" s="172" t="s">
+      <c r="H1" s="166" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="172"/>
-      <c r="J1" s="172"/>
+      <c r="I1" s="166"/>
+      <c r="J1" s="166"/>
     </row>
     <row r="2" spans="2:10">
-      <c r="H2" s="173" t="s">
+      <c r="H2" s="167" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="173"/>
-      <c r="J2" s="173"/>
+      <c r="I2" s="167"/>
+      <c r="J2" s="167"/>
     </row>
     <row r="3" spans="2:10">
       <c r="H3" s="108"/>
@@ -2904,7 +2887,7 @@
       </c>
     </row>
     <row r="6" spans="2:10">
-      <c r="B6" s="174"/>
+      <c r="B6" s="168"/>
       <c r="H6" s="108" t="s">
         <v>9</v>
       </c>
@@ -2917,140 +2900,137 @@
     </row>
     <row r="7" ht="14.45" customHeight="1"/>
     <row r="8" spans="2:10">
-      <c r="B8" s="175" t="s">
+      <c r="B8" s="169" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="9" spans="2:10">
-      <c r="B9" s="176" t="s">
+      <c r="B9" s="170" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="10" spans="2:10">
-      <c r="B10" s="176" t="s">
+      <c r="B10" s="170" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="11" spans="2:10">
-      <c r="B11" s="176" t="s">
+      <c r="B11" s="170" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="12" spans="2:10">
-      <c r="B12" s="176"/>
-      <c r="C12" s="176"/>
-      <c r="D12" s="176"/>
-      <c r="E12" s="176"/>
+      <c r="B12" s="170"/>
+      <c r="C12" s="170"/>
+      <c r="D12" s="170"/>
+      <c r="E12" s="170"/>
     </row>
     <row r="13" spans="2:10">
-      <c r="B13" s="176"/>
-      <c r="C13" s="176"/>
-      <c r="D13" s="176"/>
-      <c r="E13" s="176"/>
+      <c r="B13" s="170"/>
+      <c r="C13" s="170"/>
+      <c r="D13" s="170"/>
+      <c r="E13" s="170"/>
     </row>
     <row r="14" spans="2:10">
       <c r="B14" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="176"/>
-      <c r="D14" s="176"/>
-      <c r="E14" s="176"/>
+      <c r="C14" s="170"/>
+      <c r="D14" s="170"/>
+      <c r="E14" s="170"/>
     </row>
     <row r="15" spans="2:10">
-      <c r="B15" t="s">
+      <c r="C15" s="170"/>
+      <c r="D15" s="170"/>
+      <c r="E15" s="170"/>
+    </row>
+    <row r="16" spans="2:10">
+      <c r="B16" s="171" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="176"/>
-      <c r="D15" s="176"/>
-      <c r="E15" s="176"/>
-    </row>
-    <row r="16" spans="2:10">
-      <c r="B16" s="177" t="s">
+      <c r="C16" s="170"/>
+      <c r="D16" s="170"/>
+      <c r="E16" s="170"/>
+    </row>
+    <row r="17" spans="1:15">
+      <c r="B17" s="170"/>
+      <c r="D17" s="170"/>
+      <c r="E17" s="170"/>
+    </row>
+    <row r="18" spans="1:15">
+      <c r="B18" s="169" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="176"/>
-      <c r="D16" s="176"/>
-      <c r="E16" s="176"/>
-    </row>
-    <row r="17" spans="1:15">
-      <c r="B17" s="176"/>
-      <c r="D17" s="176"/>
-      <c r="E17" s="176"/>
-    </row>
-    <row r="18" spans="1:15">
-      <c r="B18" s="175" t="s">
+    </row>
+    <row r="19" spans="1:15">
+      <c r="B19" s="170" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:15">
-      <c r="B19" s="176" t="s">
+    <row r="20" spans="1:15">
+      <c r="C20" s="172" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:15">
-      <c r="C20" s="178" t="s">
+    <row r="21" spans="1:15">
+      <c r="B21" s="170" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:15">
-      <c r="B21" s="176" t="s">
+    <row r="22" spans="1:15">
+      <c r="B22" s="170" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="22" spans="1:15">
-      <c r="B22" s="176" t="s">
+      <c r="D22" s="170"/>
+      <c r="E22" s="170"/>
+      <c r="F22" s="170"/>
+      <c r="G22" s="170"/>
+      <c r="H22" s="170"/>
+      <c r="I22" s="170"/>
+      <c r="J22" s="170"/>
+      <c r="K22" s="170"/>
+      <c r="L22" s="170"/>
+      <c r="M22" s="170"/>
+      <c r="N22" s="170"/>
+      <c r="O22" s="170"/>
+    </row>
+    <row r="23" spans="1:15">
+      <c r="B23" s="170" t="s">
         <v>22</v>
       </c>
-      <c r="D22" s="176"/>
-      <c r="E22" s="176"/>
-      <c r="F22" s="176"/>
-      <c r="G22" s="176"/>
-      <c r="H22" s="176"/>
-      <c r="I22" s="176"/>
-      <c r="J22" s="176"/>
-      <c r="K22" s="176"/>
-      <c r="L22" s="176"/>
-      <c r="M22" s="176"/>
-      <c r="N22" s="176"/>
-      <c r="O22" s="176"/>
-    </row>
-    <row r="23" spans="1:15">
-      <c r="B23" s="176" t="s">
+      <c r="D23" s="170"/>
+      <c r="E23" s="170"/>
+      <c r="F23" s="170"/>
+      <c r="G23" s="170"/>
+      <c r="H23" s="170"/>
+      <c r="I23" s="170"/>
+      <c r="J23" s="170"/>
+      <c r="K23" s="170"/>
+      <c r="L23" s="170"/>
+      <c r="M23" s="170"/>
+      <c r="N23" s="170"/>
+      <c r="O23" s="170"/>
+    </row>
+    <row r="24" ht="14.45" customHeight="1" spans="1:15">
+      <c r="A24" s="173"/>
+      <c r="B24" s="174" t="s">
         <v>23</v>
       </c>
-      <c r="D23" s="176"/>
-      <c r="E23" s="176"/>
-      <c r="F23" s="176"/>
-      <c r="G23" s="176"/>
-      <c r="H23" s="176"/>
-      <c r="I23" s="176"/>
-      <c r="J23" s="176"/>
-      <c r="K23" s="176"/>
-      <c r="L23" s="176"/>
-      <c r="M23" s="176"/>
-      <c r="N23" s="176"/>
-      <c r="O23" s="176"/>
-    </row>
-    <row r="24" ht="14.45" customHeight="1" spans="1:15">
-      <c r="A24" s="179"/>
-      <c r="B24" s="180" t="s">
-        <v>24</v>
-      </c>
-      <c r="C24" s="180"/>
-      <c r="D24" s="180"/>
-      <c r="E24" s="180"/>
-      <c r="F24" s="180"/>
-      <c r="G24" s="180"/>
-      <c r="H24" s="180"/>
-      <c r="I24" s="180"/>
-      <c r="J24" s="180"/>
-      <c r="K24" s="180"/>
-      <c r="L24" s="180"/>
-      <c r="M24" s="180"/>
-      <c r="N24" s="180"/>
+      <c r="C24" s="174"/>
+      <c r="D24" s="174"/>
+      <c r="E24" s="174"/>
+      <c r="F24" s="174"/>
+      <c r="G24" s="174"/>
+      <c r="H24" s="174"/>
+      <c r="I24" s="174"/>
+      <c r="J24" s="174"/>
+      <c r="K24" s="174"/>
+      <c r="L24" s="174"/>
+      <c r="M24" s="174"/>
+      <c r="N24" s="174"/>
     </row>
     <row r="26" spans="1:15">
-      <c r="C26" s="181"/>
+      <c r="C26" s="175"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -3098,8 +3078,8 @@
       <c r="E1" s="3"/>
     </row>
     <row r="3" spans="2:17">
-      <c r="B3" s="164" t="s">
-        <v>17</v>
+      <c r="B3" s="161" t="s">
+        <v>16</v>
       </c>
       <c r="C3" s="111"/>
       <c r="D3" s="111"/>
@@ -3108,14 +3088,14 @@
       <c r="G3" s="112"/>
     </row>
     <row r="5" spans="2:17">
-      <c r="B5" s="165" t="s">
+      <c r="B5" s="162" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="162"/>
+      <c r="D5" s="162"/>
+      <c r="E5" s="162"/>
+      <c r="G5" s="114" t="s">
         <v>25</v>
-      </c>
-      <c r="C5" s="165"/>
-      <c r="D5" s="165"/>
-      <c r="E5" s="165"/>
-      <c r="G5" s="114" t="s">
-        <v>26</v>
       </c>
       <c r="H5" s="114"/>
       <c r="I5" s="114"/>
@@ -3130,25 +3110,25 @@
     </row>
     <row r="6" spans="2:17">
       <c r="B6" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="D6" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="E6" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="G6" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="H6" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="I6" s="9" t="s">
         <v>32</v>
-      </c>
-      <c r="I6" s="9" t="s">
-        <v>33</v>
       </c>
       <c r="J6" s="10"/>
       <c r="K6" s="10"/>
@@ -3157,7 +3137,7 @@
       <c r="N6" s="10"/>
       <c r="O6" s="11"/>
       <c r="P6" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q6" s="12"/>
     </row>
@@ -3166,33 +3146,33 @@
         <v>1</v>
       </c>
       <c r="C7" s="115" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D7" s="115" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E7" s="115"/>
       <c r="G7" s="122"/>
       <c r="H7" s="123"/>
       <c r="I7" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="J7" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="J7" s="12" t="s">
+      <c r="K7" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="K7" s="12" t="s">
+      <c r="L7" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="L7" s="12" t="s">
+      <c r="M7" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="M7" s="166" t="s">
+      <c r="N7" s="10"/>
+      <c r="O7" s="11"/>
+      <c r="P7" s="9" t="s">
         <v>40</v>
-      </c>
-      <c r="N7" s="167"/>
-      <c r="O7" s="168"/>
-      <c r="P7" s="9" t="s">
-        <v>41</v>
       </c>
       <c r="Q7" s="11"/>
     </row>
@@ -3203,74 +3183,74 @@
       <c r="C8" s="115"/>
       <c r="D8" s="115"/>
       <c r="E8" s="115" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G8" s="12">
         <v>1</v>
       </c>
       <c r="H8" s="108" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I8" s="108">
         <v>100</v>
       </c>
       <c r="J8" s="108" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K8" s="108">
         <v>15</v>
       </c>
       <c r="L8" s="108" t="s">
+        <v>44</v>
+      </c>
+      <c r="M8" s="155" t="s">
         <v>45</v>
       </c>
-      <c r="M8" s="158" t="s">
+      <c r="N8" s="156"/>
+      <c r="O8" s="157"/>
+      <c r="P8" s="163" t="s">
         <v>46</v>
       </c>
-      <c r="N8" s="159"/>
-      <c r="O8" s="160"/>
-      <c r="P8" s="169" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q8" s="170"/>
+      <c r="Q8" s="164"/>
     </row>
     <row r="9" spans="2:17">
       <c r="B9" s="115">
         <v>3</v>
       </c>
       <c r="C9" s="115" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" s="115" t="s">
         <v>48</v>
-      </c>
-      <c r="D9" s="115" t="s">
-        <v>49</v>
       </c>
       <c r="E9" s="115"/>
       <c r="G9" s="32">
         <v>2</v>
       </c>
       <c r="H9" s="36" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I9" s="36">
         <v>101</v>
       </c>
       <c r="J9" s="36" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K9" s="36">
         <v>20</v>
       </c>
       <c r="L9" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="M9" s="148" t="s">
         <v>45</v>
       </c>
-      <c r="M9" s="149" t="s">
-        <v>46</v>
-      </c>
-      <c r="N9" s="150"/>
-      <c r="O9" s="151"/>
-      <c r="P9" s="152" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q9" s="153"/>
+      <c r="N9" s="149"/>
+      <c r="O9" s="150"/>
+      <c r="P9" s="151" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q9" s="152"/>
     </row>
     <row r="10" spans="2:17">
       <c r="B10" s="115">
@@ -3279,74 +3259,74 @@
       <c r="C10" s="115"/>
       <c r="D10" s="115"/>
       <c r="E10" s="115" t="s">
+        <v>52</v>
+      </c>
+      <c r="G10" s="165">
+        <v>3</v>
+      </c>
+      <c r="H10" s="130" t="s">
         <v>53</v>
       </c>
-      <c r="G10" s="171">
-        <v>3</v>
-      </c>
-      <c r="H10" s="131" t="s">
+      <c r="I10" s="130">
+        <v>102</v>
+      </c>
+      <c r="J10" s="130" t="s">
         <v>54</v>
       </c>
-      <c r="I10" s="131">
-        <v>102</v>
-      </c>
-      <c r="J10" s="131" t="s">
+      <c r="K10" s="130">
+        <v>-5</v>
+      </c>
+      <c r="L10" s="130" t="s">
+        <v>44</v>
+      </c>
+      <c r="M10" s="131" t="s">
+        <v>45</v>
+      </c>
+      <c r="N10" s="132"/>
+      <c r="O10" s="133"/>
+      <c r="P10" s="134" t="s">
         <v>55</v>
       </c>
-      <c r="K10" s="131">
-        <v>-5</v>
-      </c>
-      <c r="L10" s="131" t="s">
-        <v>45</v>
-      </c>
-      <c r="M10" s="132" t="s">
-        <v>46</v>
-      </c>
-      <c r="N10" s="133"/>
-      <c r="O10" s="134"/>
-      <c r="P10" s="135" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q10" s="136"/>
+      <c r="Q10" s="135"/>
     </row>
     <row r="11" ht="15" customHeight="1" spans="2:17">
       <c r="B11" s="115">
         <v>5</v>
       </c>
       <c r="C11" s="115" t="s">
+        <v>56</v>
+      </c>
+      <c r="D11" s="115" t="s">
         <v>57</v>
-      </c>
-      <c r="D11" s="115" t="s">
-        <v>58</v>
       </c>
       <c r="E11" s="115"/>
       <c r="G11" s="51">
         <v>4</v>
       </c>
       <c r="H11" s="55" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I11" s="55">
         <v>103</v>
       </c>
       <c r="J11" s="55" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K11" s="55">
         <v>0</v>
       </c>
       <c r="L11" s="55" t="s">
+        <v>44</v>
+      </c>
+      <c r="M11" s="139" t="s">
         <v>45</v>
       </c>
-      <c r="M11" s="140" t="s">
-        <v>46</v>
-      </c>
-      <c r="N11" s="141"/>
-      <c r="O11" s="142"/>
-      <c r="P11" s="143" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q11" s="144"/>
+      <c r="N11" s="140"/>
+      <c r="O11" s="141"/>
+      <c r="P11" s="142" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q11" s="143"/>
     </row>
     <row r="12" spans="2:17">
       <c r="B12" s="115">
@@ -3355,7 +3335,7 @@
       <c r="C12" s="115"/>
       <c r="D12" s="115"/>
       <c r="E12" s="115" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="2:17">
@@ -3363,22 +3343,22 @@
         <v>7</v>
       </c>
       <c r="C13" s="120" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D13" s="115" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E13" s="115"/>
-      <c r="G13" s="161"/>
+      <c r="G13" s="158"/>
     </row>
     <row r="14" spans="2:17">
       <c r="B14" s="115">
         <v>8</v>
       </c>
-      <c r="C14" s="154"/>
+      <c r="C14" s="153"/>
       <c r="D14" s="115"/>
       <c r="E14" s="115" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15" spans="2:17">
@@ -3386,10 +3366,10 @@
         <v>9</v>
       </c>
       <c r="C15" s="115" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D15" s="115" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E15" s="115"/>
     </row>
@@ -3400,7 +3380,7 @@
       <c r="C16" s="115"/>
       <c r="D16" s="115"/>
       <c r="E16" s="115" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17" spans="2:6">
@@ -3408,10 +3388,10 @@
         <v>11</v>
       </c>
       <c r="C17" s="115" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D17" s="115" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E17" s="115"/>
     </row>
@@ -3422,14 +3402,14 @@
       <c r="C18" s="115"/>
       <c r="D18" s="115"/>
       <c r="E18" s="115" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20" spans="2:6">
       <c r="D20" t="s">
-        <v>68</v>
-      </c>
-      <c r="F20" s="161"/>
+        <v>67</v>
+      </c>
+      <c r="F20" s="158"/>
     </row>
   </sheetData>
   <mergeCells count="24">
@@ -3499,7 +3479,7 @@
     </row>
     <row r="3" spans="2:18">
       <c r="B3" s="110" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C3" s="111"/>
       <c r="D3" s="111"/>
@@ -3509,13 +3489,13 @@
     </row>
     <row r="5" spans="2:18">
       <c r="B5" s="113" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C5" s="113"/>
       <c r="D5" s="113"/>
       <c r="E5" s="84"/>
       <c r="G5" s="114" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H5" s="114"/>
       <c r="I5" s="114"/>
@@ -3531,29 +3511,29 @@
     </row>
     <row r="6" ht="14.45" customHeight="1" spans="2:18">
       <c r="B6" s="115" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C6" s="115" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D6" s="115" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E6" s="116"/>
       <c r="G6" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H6" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="I6" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="I6" s="5" t="s">
+      <c r="J6" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="J6" s="8" t="s">
-        <v>76</v>
-      </c>
       <c r="K6" s="117" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L6" s="118"/>
       <c r="M6" s="118"/>
@@ -3561,7 +3541,7 @@
       <c r="O6" s="118"/>
       <c r="P6" s="119"/>
       <c r="Q6" s="117" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="R6" s="119"/>
     </row>
@@ -3570,379 +3550,379 @@
         <v>1</v>
       </c>
       <c r="C7" s="121" t="s">
+        <v>76</v>
+      </c>
+      <c r="D7" s="108" t="s">
         <v>77</v>
-      </c>
-      <c r="D7" s="108" t="s">
-        <v>78</v>
       </c>
       <c r="G7" s="122"/>
       <c r="H7" s="122"/>
       <c r="I7" s="122"/>
       <c r="J7" s="123"/>
       <c r="K7" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="L7" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="L7" s="12" t="s">
+      <c r="M7" s="92" t="s">
         <v>38</v>
       </c>
-      <c r="M7" s="92" t="s">
+      <c r="N7" s="90" t="s">
         <v>39</v>
       </c>
-      <c r="N7" s="124" t="s">
-        <v>40</v>
-      </c>
-      <c r="O7" s="125"/>
-      <c r="P7" s="126"/>
+      <c r="O7" s="124"/>
+      <c r="P7" s="125"/>
       <c r="Q7" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="R7" s="11"/>
+    </row>
+    <row r="8" spans="2:18">
+      <c r="B8" s="126"/>
+      <c r="C8" s="127"/>
+      <c r="D8" s="108" t="s">
         <v>79</v>
-      </c>
-      <c r="R7" s="11"/>
-    </row>
-    <row r="8" spans="2:18">
-      <c r="B8" s="127"/>
-      <c r="C8" s="128"/>
-      <c r="D8" s="108" t="s">
-        <v>80</v>
       </c>
       <c r="G8" s="12">
         <v>1</v>
       </c>
-      <c r="H8" s="182" t="s">
+      <c r="H8" s="176" t="s">
+        <v>80</v>
+      </c>
+      <c r="I8" s="129" t="s">
         <v>81</v>
       </c>
-      <c r="I8" s="130" t="s">
-        <v>82</v>
-      </c>
-      <c r="J8" s="130"/>
-      <c r="K8" s="131" t="s">
+      <c r="J8" s="129"/>
+      <c r="K8" s="130" t="s">
+        <v>50</v>
+      </c>
+      <c r="L8" s="130">
+        <v>15.1</v>
+      </c>
+      <c r="M8" s="130" t="s">
+        <v>44</v>
+      </c>
+      <c r="N8" s="131" t="s">
+        <v>45</v>
+      </c>
+      <c r="O8" s="132"/>
+      <c r="P8" s="133"/>
+      <c r="Q8" s="134" t="s">
         <v>51</v>
       </c>
-      <c r="L8" s="131">
-        <v>15.1</v>
-      </c>
-      <c r="M8" s="131" t="s">
-        <v>45</v>
-      </c>
-      <c r="N8" s="132" t="s">
-        <v>46</v>
-      </c>
-      <c r="O8" s="133"/>
-      <c r="P8" s="134"/>
-      <c r="Q8" s="135" t="s">
-        <v>52</v>
-      </c>
-      <c r="R8" s="136"/>
+      <c r="R8" s="135"/>
     </row>
     <row r="9" spans="2:18">
-      <c r="B9" s="127"/>
-      <c r="C9" s="128"/>
+      <c r="B9" s="126"/>
+      <c r="C9" s="127"/>
       <c r="D9" s="108"/>
       <c r="G9" s="51">
         <v>2</v>
       </c>
-      <c r="H9" s="183" t="s">
+      <c r="H9" s="177" t="s">
+        <v>82</v>
+      </c>
+      <c r="I9" s="137" t="s">
         <v>83</v>
       </c>
-      <c r="I9" s="138" t="s">
+      <c r="J9" s="137"/>
+      <c r="K9" s="138" t="s">
         <v>84</v>
-      </c>
-      <c r="J9" s="138"/>
-      <c r="K9" s="139" t="s">
-        <v>85</v>
       </c>
       <c r="L9" s="55">
         <v>15.1</v>
       </c>
       <c r="M9" s="55" t="s">
+        <v>44</v>
+      </c>
+      <c r="N9" s="139" t="s">
         <v>45</v>
       </c>
-      <c r="N9" s="140" t="s">
+      <c r="O9" s="140"/>
+      <c r="P9" s="141"/>
+      <c r="Q9" s="142" t="s">
         <v>46</v>
       </c>
-      <c r="O9" s="141"/>
-      <c r="P9" s="142"/>
-      <c r="Q9" s="143" t="s">
-        <v>47</v>
-      </c>
-      <c r="R9" s="144"/>
+      <c r="R9" s="143"/>
     </row>
     <row r="10" spans="2:18">
-      <c r="B10" s="127"/>
-      <c r="C10" s="128"/>
+      <c r="B10" s="126"/>
+      <c r="C10" s="127"/>
       <c r="D10" s="108"/>
       <c r="G10" s="12">
         <v>3</v>
       </c>
-      <c r="H10" s="182" t="s">
+      <c r="H10" s="176" t="s">
+        <v>85</v>
+      </c>
+      <c r="I10" s="129" t="s">
         <v>86</v>
       </c>
-      <c r="I10" s="130" t="s">
+      <c r="J10" s="129"/>
+      <c r="K10" s="144" t="s">
         <v>87</v>
       </c>
-      <c r="J10" s="130"/>
-      <c r="K10" s="145" t="s">
-        <v>88</v>
-      </c>
-      <c r="L10" s="131">
+      <c r="L10" s="130">
         <v>15.1</v>
       </c>
-      <c r="M10" s="131" t="s">
+      <c r="M10" s="130" t="s">
+        <v>44</v>
+      </c>
+      <c r="N10" s="131" t="s">
         <v>45</v>
       </c>
-      <c r="N10" s="132" t="s">
+      <c r="O10" s="132"/>
+      <c r="P10" s="133"/>
+      <c r="Q10" s="134" t="s">
         <v>46</v>
       </c>
-      <c r="O10" s="133"/>
-      <c r="P10" s="134"/>
-      <c r="Q10" s="135" t="s">
-        <v>47</v>
-      </c>
-      <c r="R10" s="136"/>
+      <c r="R10" s="135"/>
     </row>
     <row r="11" spans="2:18">
-      <c r="B11" s="127"/>
-      <c r="C11" s="128"/>
+      <c r="B11" s="126"/>
+      <c r="C11" s="127"/>
       <c r="D11" s="108"/>
       <c r="G11" s="32">
         <v>4</v>
       </c>
-      <c r="H11" s="184" t="s">
+      <c r="H11" s="178" t="s">
+        <v>88</v>
+      </c>
+      <c r="I11" s="146" t="s">
         <v>89</v>
       </c>
-      <c r="I11" s="147" t="s">
+      <c r="J11" s="146"/>
+      <c r="K11" s="147" t="s">
         <v>90</v>
-      </c>
-      <c r="J11" s="147"/>
-      <c r="K11" s="148" t="s">
-        <v>91</v>
       </c>
       <c r="L11" s="36">
         <v>15.1</v>
       </c>
       <c r="M11" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="N11" s="148" t="s">
         <v>45</v>
       </c>
-      <c r="N11" s="149" t="s">
+      <c r="O11" s="149"/>
+      <c r="P11" s="150"/>
+      <c r="Q11" s="151" t="s">
         <v>46</v>
       </c>
-      <c r="O11" s="150"/>
-      <c r="P11" s="151"/>
-      <c r="Q11" s="152" t="s">
-        <v>47</v>
-      </c>
-      <c r="R11" s="153"/>
+      <c r="R11" s="152"/>
     </row>
     <row r="12" spans="2:18">
-      <c r="B12" s="154"/>
-      <c r="C12" s="155"/>
+      <c r="B12" s="153"/>
+      <c r="C12" s="154"/>
       <c r="D12" s="108"/>
       <c r="G12" s="12">
         <v>5</v>
       </c>
-      <c r="H12" s="182" t="s">
+      <c r="H12" s="176" t="s">
+        <v>91</v>
+      </c>
+      <c r="I12" s="129" t="s">
         <v>92</v>
       </c>
-      <c r="I12" s="130" t="s">
+      <c r="J12" s="129"/>
+      <c r="K12" s="144" t="s">
         <v>93</v>
       </c>
-      <c r="J12" s="130"/>
-      <c r="K12" s="145" t="s">
+      <c r="L12" s="130">
+        <v>15.1</v>
+      </c>
+      <c r="M12" s="130" t="s">
+        <v>44</v>
+      </c>
+      <c r="N12" s="131" t="s">
+        <v>45</v>
+      </c>
+      <c r="O12" s="132"/>
+      <c r="P12" s="133"/>
+      <c r="Q12" s="134" t="s">
         <v>94</v>
       </c>
-      <c r="L12" s="131">
-        <v>15.1</v>
-      </c>
-      <c r="M12" s="131" t="s">
-        <v>45</v>
-      </c>
-      <c r="N12" s="132" t="s">
-        <v>46</v>
-      </c>
-      <c r="O12" s="133"/>
-      <c r="P12" s="134"/>
-      <c r="Q12" s="135" t="s">
-        <v>95</v>
-      </c>
-      <c r="R12" s="136"/>
+      <c r="R12" s="135"/>
     </row>
     <row r="13" spans="2:18">
       <c r="B13" s="120">
         <v>2</v>
       </c>
       <c r="C13" s="120" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D13" s="108" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G13" s="51">
         <v>6</v>
       </c>
-      <c r="H13" s="183" t="s">
+      <c r="H13" s="177" t="s">
+        <v>96</v>
+      </c>
+      <c r="I13" s="137" t="s">
         <v>97</v>
       </c>
-      <c r="I13" s="138" t="s">
-        <v>98</v>
-      </c>
-      <c r="J13" s="138"/>
-      <c r="K13" s="139" t="s">
-        <v>55</v>
+      <c r="J13" s="137"/>
+      <c r="K13" s="138" t="s">
+        <v>54</v>
       </c>
       <c r="L13" s="55">
         <v>0</v>
       </c>
       <c r="M13" s="55" t="s">
+        <v>44</v>
+      </c>
+      <c r="N13" s="139" t="s">
         <v>45</v>
       </c>
-      <c r="N13" s="140" t="s">
-        <v>46</v>
-      </c>
-      <c r="O13" s="141"/>
-      <c r="P13" s="142"/>
-      <c r="Q13" s="143" t="s">
-        <v>60</v>
-      </c>
-      <c r="R13" s="144"/>
+      <c r="O13" s="140"/>
+      <c r="P13" s="141"/>
+      <c r="Q13" s="142" t="s">
+        <v>59</v>
+      </c>
+      <c r="R13" s="143"/>
     </row>
     <row r="14" spans="2:18">
-      <c r="B14" s="127"/>
-      <c r="C14" s="127"/>
+      <c r="B14" s="126"/>
+      <c r="C14" s="126"/>
       <c r="D14" s="108" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G14" s="12">
         <v>7</v>
       </c>
-      <c r="H14" s="182" t="s">
+      <c r="H14" s="176" t="s">
+        <v>99</v>
+      </c>
+      <c r="I14" s="129" t="s">
         <v>100</v>
       </c>
-      <c r="I14" s="130" t="s">
+      <c r="J14" s="129"/>
+      <c r="K14" s="108" t="s">
+        <v>54</v>
+      </c>
+      <c r="L14" s="133">
+        <v>0.01</v>
+      </c>
+      <c r="M14" s="130" t="s">
+        <v>44</v>
+      </c>
+      <c r="N14" s="131" t="s">
+        <v>45</v>
+      </c>
+      <c r="O14" s="132"/>
+      <c r="P14" s="133"/>
+      <c r="Q14" s="134" t="s">
+        <v>46</v>
+      </c>
+      <c r="R14" s="135"/>
+    </row>
+    <row r="15" spans="2:18">
+      <c r="B15" s="126"/>
+      <c r="C15" s="126"/>
+      <c r="D15" s="108" t="s">
         <v>101</v>
-      </c>
-      <c r="J14" s="130"/>
-      <c r="K14" s="108" t="s">
-        <v>55</v>
-      </c>
-      <c r="L14" s="156">
-        <v>0.01</v>
-      </c>
-      <c r="M14" s="131" t="s">
-        <v>45</v>
-      </c>
-      <c r="N14" s="132" t="s">
-        <v>46</v>
-      </c>
-      <c r="O14" s="133"/>
-      <c r="P14" s="134"/>
-      <c r="Q14" s="135" t="s">
-        <v>47</v>
-      </c>
-      <c r="R14" s="136"/>
-    </row>
-    <row r="15" spans="2:18">
-      <c r="B15" s="127"/>
-      <c r="C15" s="127"/>
-      <c r="D15" s="108" t="s">
-        <v>102</v>
       </c>
       <c r="G15" s="32">
         <v>8</v>
       </c>
-      <c r="H15" s="184" t="s">
+      <c r="H15" s="178" t="s">
+        <v>102</v>
+      </c>
+      <c r="I15" s="146" t="s">
         <v>103</v>
       </c>
-      <c r="I15" s="147" t="s">
-        <v>104</v>
-      </c>
-      <c r="J15" s="147"/>
+      <c r="J15" s="146"/>
       <c r="K15" s="36" t="s">
-        <v>55</v>
-      </c>
-      <c r="L15" s="157">
+        <v>54</v>
+      </c>
+      <c r="L15" s="150">
         <v>9999.99</v>
       </c>
       <c r="M15" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="N15" s="148" t="s">
         <v>45</v>
       </c>
-      <c r="N15" s="149" t="s">
+      <c r="O15" s="149"/>
+      <c r="P15" s="150"/>
+      <c r="Q15" s="151" t="s">
         <v>46</v>
       </c>
-      <c r="O15" s="150"/>
-      <c r="P15" s="151"/>
-      <c r="Q15" s="152" t="s">
-        <v>47</v>
-      </c>
-      <c r="R15" s="153"/>
+      <c r="R15" s="152"/>
     </row>
     <row r="16" spans="2:18">
-      <c r="B16" s="127"/>
-      <c r="C16" s="127"/>
+      <c r="B16" s="126"/>
+      <c r="C16" s="126"/>
       <c r="D16" s="108"/>
       <c r="G16" s="12">
         <v>9</v>
       </c>
-      <c r="H16" s="182" t="s">
+      <c r="H16" s="176" t="s">
+        <v>104</v>
+      </c>
+      <c r="I16" s="129" t="s">
         <v>105</v>
       </c>
-      <c r="I16" s="130" t="s">
-        <v>106</v>
-      </c>
-      <c r="J16" s="130"/>
+      <c r="J16" s="129"/>
       <c r="K16" s="108" t="s">
-        <v>55</v>
-      </c>
-      <c r="L16" s="156">
+        <v>54</v>
+      </c>
+      <c r="L16" s="133">
         <v>10000</v>
       </c>
-      <c r="M16" s="131" t="s">
+      <c r="M16" s="130" t="s">
+        <v>44</v>
+      </c>
+      <c r="N16" s="155" t="s">
         <v>45</v>
       </c>
-      <c r="N16" s="158" t="s">
+      <c r="O16" s="156"/>
+      <c r="P16" s="157"/>
+      <c r="Q16" s="134" t="s">
         <v>46</v>
       </c>
-      <c r="O16" s="159"/>
-      <c r="P16" s="160"/>
-      <c r="Q16" s="135" t="s">
-        <v>47</v>
-      </c>
-      <c r="R16" s="136"/>
+      <c r="R16" s="135"/>
     </row>
     <row r="17" spans="2:18">
-      <c r="B17" s="127"/>
-      <c r="C17" s="127"/>
+      <c r="B17" s="126"/>
+      <c r="C17" s="126"/>
       <c r="D17" s="108"/>
       <c r="G17" s="51">
         <v>10</v>
       </c>
-      <c r="H17" s="137">
+      <c r="H17" s="136">
         <v>10</v>
       </c>
-      <c r="I17" s="138" t="s">
-        <v>107</v>
-      </c>
-      <c r="J17" s="138"/>
+      <c r="I17" s="137" t="s">
+        <v>106</v>
+      </c>
+      <c r="J17" s="137"/>
       <c r="K17" s="55" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L17" s="55">
         <v>10000.01</v>
       </c>
       <c r="M17" s="55" t="s">
+        <v>44</v>
+      </c>
+      <c r="N17" s="139" t="s">
         <v>45</v>
       </c>
-      <c r="N17" s="140" t="s">
-        <v>46</v>
-      </c>
-      <c r="O17" s="141"/>
-      <c r="P17" s="142"/>
-      <c r="Q17" s="143" t="s">
-        <v>108</v>
-      </c>
-      <c r="R17" s="144"/>
+      <c r="O17" s="140"/>
+      <c r="P17" s="141"/>
+      <c r="Q17" s="142" t="s">
+        <v>107</v>
+      </c>
+      <c r="R17" s="143"/>
     </row>
     <row r="18" spans="2:18">
-      <c r="B18" s="154"/>
-      <c r="C18" s="154"/>
+      <c r="B18" s="153"/>
+      <c r="C18" s="153"/>
       <c r="D18" s="108"/>
     </row>
     <row r="19" spans="2:18">
@@ -3950,51 +3930,51 @@
         <v>3</v>
       </c>
       <c r="C19" s="121" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D19" s="108" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="20" spans="2:18">
+      <c r="B20" s="126"/>
+      <c r="C20" s="127"/>
+      <c r="D20" s="108" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="20" spans="2:18">
-      <c r="B20" s="127"/>
-      <c r="C20" s="128"/>
-      <c r="D20" s="108" t="s">
-        <v>110</v>
-      </c>
-      <c r="G20" s="161"/>
-      <c r="H20" s="161"/>
-      <c r="I20" s="162"/>
-      <c r="J20" s="162"/>
-      <c r="K20" s="162"/>
-      <c r="L20" s="162"/>
-      <c r="M20" s="162"/>
-      <c r="N20" s="162"/>
+      <c r="G20" s="158"/>
+      <c r="H20" s="158"/>
+      <c r="I20" s="159"/>
+      <c r="J20" s="159"/>
+      <c r="K20" s="159"/>
+      <c r="L20" s="159"/>
+      <c r="M20" s="159"/>
+      <c r="N20" s="159"/>
     </row>
     <row r="21" spans="2:18">
-      <c r="B21" s="127"/>
-      <c r="C21" s="128"/>
+      <c r="B21" s="126"/>
+      <c r="C21" s="127"/>
       <c r="D21" s="108"/>
-      <c r="I21" s="163"/>
-      <c r="J21" s="163"/>
-      <c r="K21" s="163"/>
-      <c r="L21" s="163"/>
-      <c r="M21" s="163"/>
-      <c r="N21" s="163"/>
+      <c r="I21" s="160"/>
+      <c r="J21" s="160"/>
+      <c r="K21" s="160"/>
+      <c r="L21" s="160"/>
+      <c r="M21" s="160"/>
+      <c r="N21" s="160"/>
     </row>
     <row r="22" spans="2:18">
-      <c r="B22" s="127"/>
-      <c r="C22" s="128"/>
+      <c r="B22" s="126"/>
+      <c r="C22" s="127"/>
       <c r="D22" s="108"/>
     </row>
     <row r="23" spans="2:18">
-      <c r="B23" s="127"/>
-      <c r="C23" s="128"/>
+      <c r="B23" s="126"/>
+      <c r="C23" s="127"/>
       <c r="D23" s="108"/>
     </row>
     <row r="24" spans="2:18">
-      <c r="B24" s="154"/>
-      <c r="C24" s="155"/>
+      <c r="B24" s="153"/>
+      <c r="C24" s="154"/>
       <c r="D24" s="108"/>
     </row>
     <row r="25" spans="2:18">
@@ -4002,39 +3982,39 @@
         <v>4</v>
       </c>
       <c r="C25" s="121" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D25" s="108" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="26" spans="2:18">
+      <c r="B26" s="126"/>
+      <c r="C26" s="127"/>
+      <c r="D26" s="108" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="26" spans="2:18">
-      <c r="B26" s="127"/>
-      <c r="C26" s="128"/>
-      <c r="D26" s="108" t="s">
+    <row r="27" spans="2:18">
+      <c r="B27" s="126"/>
+      <c r="C27" s="127"/>
+      <c r="D27" s="108" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="27" spans="2:18">
-      <c r="B27" s="127"/>
-      <c r="C27" s="128"/>
-      <c r="D27" s="108" t="s">
-        <v>113</v>
-      </c>
-    </row>
     <row r="28" spans="2:18">
-      <c r="B28" s="127"/>
-      <c r="C28" s="128"/>
+      <c r="B28" s="126"/>
+      <c r="C28" s="127"/>
       <c r="D28" s="108"/>
     </row>
     <row r="29" spans="2:18">
-      <c r="B29" s="127"/>
-      <c r="C29" s="128"/>
+      <c r="B29" s="126"/>
+      <c r="C29" s="127"/>
       <c r="D29" s="108"/>
     </row>
     <row r="30" spans="2:18">
-      <c r="B30" s="154"/>
-      <c r="C30" s="155"/>
+      <c r="B30" s="153"/>
+      <c r="C30" s="154"/>
       <c r="D30" s="108"/>
     </row>
   </sheetData>
@@ -4120,7 +4100,7 @@
     </row>
     <row r="3" spans="2:14">
       <c r="B3" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
@@ -4137,19 +4117,19 @@
     </row>
     <row r="4" spans="2:14">
       <c r="B4" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="D4" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="E4" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="E4" s="8" t="s">
-        <v>118</v>
-      </c>
       <c r="F4" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G4" s="10"/>
       <c r="H4" s="10"/>
@@ -4158,7 +4138,7 @@
       <c r="K4" s="10"/>
       <c r="L4" s="11"/>
       <c r="M4" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N4" s="12"/>
     </row>
@@ -4168,27 +4148,27 @@
       <c r="D5" s="15"/>
       <c r="E5" s="16"/>
       <c r="F5" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="G5" s="17" t="s">
+      <c r="H5" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="H5" s="17" t="s">
+      <c r="I5" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="I5" s="8" t="s">
+      <c r="J5" s="18" t="s">
         <v>39</v>
-      </c>
-      <c r="J5" s="18" t="s">
-        <v>40</v>
       </c>
       <c r="K5" s="19"/>
       <c r="L5" s="20"/>
       <c r="M5" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N5" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="6" ht="15.15" spans="2:14">
@@ -4196,33 +4176,33 @@
         <v>1</v>
       </c>
       <c r="C6" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="D6" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="E6" s="21" t="s">
         <v>121</v>
-      </c>
-      <c r="E6" s="21" t="s">
-        <v>122</v>
       </c>
       <c r="F6" s="23">
         <v>100</v>
       </c>
       <c r="G6" s="24" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H6" s="25">
         <v>15.1</v>
       </c>
       <c r="I6" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="J6" s="27" t="s">
         <v>45</v>
-      </c>
-      <c r="J6" s="27" t="s">
-        <v>46</v>
       </c>
       <c r="K6" s="28"/>
       <c r="L6" s="29"/>
       <c r="M6" s="30" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N6" s="21"/>
     </row>
@@ -4233,30 +4213,30 @@
       </c>
       <c r="C7" s="22"/>
       <c r="D7" s="32" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E7" s="31" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F7" s="33">
         <v>101</v>
       </c>
       <c r="G7" s="34" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H7" s="35">
         <v>20.1</v>
       </c>
       <c r="I7" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="J7" s="37" t="s">
         <v>45</v>
-      </c>
-      <c r="J7" s="37" t="s">
-        <v>46</v>
       </c>
       <c r="K7" s="38"/>
       <c r="L7" s="39"/>
       <c r="M7" s="40" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="N7" s="31"/>
     </row>
@@ -4267,30 +4247,30 @@
       </c>
       <c r="C8" s="22"/>
       <c r="D8" s="12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E8" s="41" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F8" s="42">
         <v>102</v>
       </c>
       <c r="G8" s="43" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H8" s="44">
         <v>-5.1</v>
       </c>
       <c r="I8" s="45" t="s">
+        <v>44</v>
+      </c>
+      <c r="J8" s="46" t="s">
         <v>45</v>
-      </c>
-      <c r="J8" s="46" t="s">
-        <v>46</v>
       </c>
       <c r="K8" s="47"/>
       <c r="L8" s="48"/>
       <c r="M8" s="49" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N8" s="41"/>
     </row>
@@ -4301,30 +4281,30 @@
       </c>
       <c r="C9" s="22"/>
       <c r="D9" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E9" s="50" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F9" s="52">
         <v>103</v>
       </c>
       <c r="G9" s="53" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H9" s="54">
         <v>0</v>
       </c>
       <c r="I9" s="55" t="s">
+        <v>44</v>
+      </c>
+      <c r="J9" s="56" t="s">
         <v>45</v>
-      </c>
-      <c r="J9" s="56" t="s">
-        <v>46</v>
       </c>
       <c r="K9" s="57"/>
       <c r="L9" s="58"/>
       <c r="M9" s="52" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="N9" s="50"/>
     </row>
@@ -4335,30 +4315,30 @@
       </c>
       <c r="C10" s="22"/>
       <c r="D10" s="12" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E10" s="41" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F10" s="42">
         <v>104</v>
       </c>
       <c r="G10" s="59" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H10" s="44">
         <v>15.1</v>
       </c>
       <c r="I10" s="45" t="s">
+        <v>44</v>
+      </c>
+      <c r="J10" s="46" t="s">
         <v>45</v>
-      </c>
-      <c r="J10" s="46" t="s">
-        <v>46</v>
       </c>
       <c r="K10" s="47"/>
       <c r="L10" s="48"/>
       <c r="M10" s="49" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N10" s="41"/>
     </row>
@@ -4369,30 +4349,30 @@
       </c>
       <c r="C11" s="22"/>
       <c r="D11" s="32" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E11" s="31" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F11" s="33">
         <v>105</v>
       </c>
       <c r="G11" s="60" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H11" s="35">
         <v>15.1</v>
       </c>
       <c r="I11" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="J11" s="37" t="s">
         <v>45</v>
-      </c>
-      <c r="J11" s="37" t="s">
-        <v>46</v>
       </c>
       <c r="K11" s="38"/>
       <c r="L11" s="39"/>
       <c r="M11" s="40" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N11" s="31"/>
     </row>
@@ -4403,30 +4383,30 @@
       </c>
       <c r="C12" s="22"/>
       <c r="D12" s="12" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E12" s="41" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F12" s="42">
         <v>106</v>
       </c>
       <c r="G12" s="43" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H12" s="62">
         <v>15.1</v>
       </c>
       <c r="I12" s="45" t="s">
+        <v>44</v>
+      </c>
+      <c r="J12" s="46" t="s">
         <v>45</v>
-      </c>
-      <c r="J12" s="46" t="s">
-        <v>46</v>
       </c>
       <c r="K12" s="47"/>
       <c r="L12" s="48"/>
       <c r="M12" s="49" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N12" s="41"/>
     </row>
@@ -4437,30 +4417,30 @@
       </c>
       <c r="C13" s="22"/>
       <c r="D13" s="51" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E13" s="63" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F13" s="64">
         <v>107</v>
       </c>
       <c r="G13" s="65" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H13" s="66">
         <v>15.1</v>
       </c>
       <c r="I13" s="55" t="s">
+        <v>44</v>
+      </c>
+      <c r="J13" s="67" t="s">
         <v>45</v>
-      </c>
-      <c r="J13" s="67" t="s">
-        <v>46</v>
       </c>
       <c r="K13" s="68"/>
       <c r="L13" s="69"/>
       <c r="M13" s="64" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N13" s="63"/>
     </row>
@@ -4470,30 +4450,30 @@
       </c>
       <c r="C14" s="22"/>
       <c r="D14" s="12" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E14" s="41" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F14" s="42">
         <v>108</v>
       </c>
       <c r="G14" s="70" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H14" s="71">
         <v>0.01</v>
       </c>
       <c r="I14" s="45" t="s">
+        <v>44</v>
+      </c>
+      <c r="J14" s="72" t="s">
         <v>45</v>
-      </c>
-      <c r="J14" s="72" t="s">
-        <v>46</v>
       </c>
       <c r="K14" s="73"/>
       <c r="L14" s="74"/>
       <c r="M14" s="42" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N14" s="41"/>
     </row>
@@ -4503,30 +4483,30 @@
       </c>
       <c r="C15" s="22"/>
       <c r="D15" s="32" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E15" s="31" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F15" s="33">
         <v>109</v>
       </c>
       <c r="G15" s="75" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H15" s="76">
         <v>9999.99</v>
       </c>
       <c r="I15" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="J15" s="77" t="s">
         <v>45</v>
-      </c>
-      <c r="J15" s="77" t="s">
-        <v>46</v>
       </c>
       <c r="K15" s="78"/>
       <c r="L15" s="79"/>
       <c r="M15" s="33" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N15" s="31"/>
     </row>
@@ -4536,30 +4516,30 @@
       </c>
       <c r="C16" s="22"/>
       <c r="D16" s="12" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E16" s="41" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F16" s="42">
         <v>110</v>
       </c>
       <c r="G16" s="70" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H16" s="71">
         <v>10000</v>
       </c>
       <c r="I16" s="45" t="s">
+        <v>44</v>
+      </c>
+      <c r="J16" s="72" t="s">
         <v>45</v>
-      </c>
-      <c r="J16" s="72" t="s">
-        <v>46</v>
       </c>
       <c r="K16" s="73"/>
       <c r="L16" s="74"/>
       <c r="M16" s="42" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N16" s="41"/>
     </row>
@@ -4569,30 +4549,30 @@
       </c>
       <c r="C17" s="80"/>
       <c r="D17" s="51" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E17" s="50" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F17" s="52">
         <v>111</v>
       </c>
       <c r="G17" s="53" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H17" s="54">
         <v>10000.01</v>
       </c>
       <c r="I17" s="55" t="s">
+        <v>44</v>
+      </c>
+      <c r="J17" s="56" t="s">
         <v>45</v>
-      </c>
-      <c r="J17" s="56" t="s">
-        <v>46</v>
       </c>
       <c r="K17" s="57"/>
       <c r="L17" s="58"/>
       <c r="M17" s="52" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N17" s="50"/>
     </row>
@@ -4613,7 +4593,7 @@
     </row>
     <row r="19" ht="14.45" customHeight="1" spans="2:16">
       <c r="B19" s="81" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C19" s="81"/>
       <c r="D19" s="82"/>
@@ -4632,23 +4612,23 @@
     </row>
     <row r="21" ht="15.15" spans="2:16">
       <c r="C21" s="85" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D21" s="86"/>
       <c r="E21" s="86"/>
       <c r="F21" s="87"/>
       <c r="G21" s="88" t="s">
+        <v>129</v>
+      </c>
+      <c r="H21" s="85" t="s">
         <v>130</v>
-      </c>
-      <c r="H21" s="85" t="s">
-        <v>131</v>
       </c>
       <c r="I21" s="89"/>
       <c r="J21" s="86"/>
       <c r="K21" s="86"/>
       <c r="L21" s="87"/>
       <c r="M21" s="85" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="N21" s="89"/>
       <c r="O21" s="86"/>
@@ -4656,47 +4636,47 @@
     </row>
     <row r="22" ht="14.45" customHeight="1" spans="2:16">
       <c r="B22" s="90" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C22" s="91" t="s">
+        <v>132</v>
+      </c>
+      <c r="D22" s="92" t="s">
         <v>133</v>
       </c>
-      <c r="D22" s="92" t="s">
+      <c r="E22" s="92" t="s">
         <v>134</v>
       </c>
-      <c r="E22" s="92" t="s">
+      <c r="F22" s="93" t="s">
         <v>135</v>
       </c>
-      <c r="F22" s="93" t="s">
+      <c r="G22" s="94" t="s">
         <v>136</v>
       </c>
-      <c r="G22" s="94" t="s">
+      <c r="H22" s="95" t="s">
         <v>137</v>
-      </c>
-      <c r="H22" s="95" t="s">
-        <v>138</v>
       </c>
       <c r="I22" s="96"/>
       <c r="J22" s="92" t="s">
+        <v>132</v>
+      </c>
+      <c r="K22" s="92" t="s">
         <v>133</v>
       </c>
-      <c r="K22" s="92" t="s">
-        <v>134</v>
-      </c>
       <c r="L22" s="93" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M22" s="97" t="s">
+        <v>137</v>
+      </c>
+      <c r="N22" s="92" t="s">
+        <v>132</v>
+      </c>
+      <c r="O22" s="92" t="s">
+        <v>133</v>
+      </c>
+      <c r="P22" s="93" t="s">
         <v>138</v>
-      </c>
-      <c r="N22" s="92" t="s">
-        <v>133</v>
-      </c>
-      <c r="O22" s="92" t="s">
-        <v>134</v>
-      </c>
-      <c r="P22" s="93" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="23" spans="2:16">
@@ -4718,7 +4698,7 @@
     </row>
     <row r="24" spans="2:16">
       <c r="B24" s="101" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C24" s="102">
         <v>12</v>
@@ -4736,7 +4716,7 @@
         <v>2</v>
       </c>
       <c r="H24" s="106" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I24" s="107"/>
       <c r="J24" s="108">
@@ -4749,7 +4729,7 @@
         <v>0</v>
       </c>
       <c r="M24" s="109" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="N24" s="108">
         <v>12</v>
@@ -4766,12 +4746,12 @@
     </row>
     <row r="26" spans="2:16">
       <c r="B26" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="27" spans="2:16">
       <c r="B27" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>
